--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79539</v>
+        <v>79540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145926</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136145917</v>
       </c>
       <c r="B9" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136145910</v>
       </c>
       <c r="B10" t="n">
-        <v>58846</v>
+        <v>58847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79540</v>
+        <v>79544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145926</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136145917</v>
       </c>
       <c r="B9" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136145910</v>
       </c>
       <c r="B10" t="n">
-        <v>58847</v>
+        <v>58851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79544</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145926</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136145917</v>
       </c>
       <c r="B9" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136145910</v>
       </c>
       <c r="B10" t="n">
-        <v>58851</v>
+        <v>58852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145926</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136145917</v>
       </c>
       <c r="B9" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136145910</v>
       </c>
       <c r="B10" t="n">
-        <v>58852</v>
+        <v>58857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145926</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136145917</v>
       </c>
       <c r="B9" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136145910</v>
       </c>
       <c r="B10" t="n">
-        <v>58857</v>
+        <v>58870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
